--- a/XLibur.Tests/Resource/Other/PivotTable/Style/Set_pivot_field_subtotals_style.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Style/Set_pivot_field_subtotals_style.xlsx
@@ -130,22 +130,24 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="3">
-    <pivotField name="Name" axis="axisRow" subtotalTop="0" showAll="0" defaultSubtotal="0" sumSubtotal="1">
-      <items count="3">
+    <pivotField name="Name" axis="axisRow" subtotalTop="0" showAll="0" sumSubtotal="1">
+      <items count="4">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
         <item t="sum"/>
       </items>
     </pivotField>
-    <pivotField name="Month" axis="axisRow" subtotalTop="0" showAll="0" defaultSubtotal="0" maxSubtotal="1" minSubtotal="1">
-      <items count="4">
+    <pivotField name="Month" axis="axisRow" subtotalTop="0" showAll="0" maxSubtotal="1" minSubtotal="1">
+      <items count="5">
         <item x="0"/>
         <item x="1"/>
+        <item t="default"/>
         <item t="max"/>
         <item t="min"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>
@@ -158,14 +160,14 @@
     <format dxfId="0">
       <pivotArea outline="0">
         <references count="1">
-          <reference field="0" count="0" sumSubtotal="1"/>
+          <reference field="0" count="0" defaultSubtotal="1" sumSubtotal="1"/>
         </references>
       </pivotArea>
     </format>
     <format dxfId="1">
       <pivotArea outline="0">
         <references count="1">
-          <reference field="1" count="0" maxSubtotal="1" minSubtotal="1"/>
+          <reference field="1" count="0" defaultSubtotal="1" maxSubtotal="1" minSubtotal="1"/>
         </references>
       </pivotArea>
     </format>

--- a/XLibur.Tests/Resource/Other/PivotTable/Style/Set_pivot_field_subtotals_style.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTable/Style/Set_pivot_field_subtotals_style.xlsx
@@ -127,7 +127,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" outline="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="pivot table" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" updatedVersion="5" minRefreshableVersion="3" createdVersion="5" outline="1">
   <location ref="A1" firstHeaderRow="0" firstDataRow="0" firstDataCol="0"/>
   <pivotFields count="3">
     <pivotField name="Name" axis="axisRow" subtotalTop="0" showAll="0" sumSubtotal="1">
